--- a/public/assets/templates/grad-law-portfolio-checklist.xlsx
+++ b/public/assets/templates/grad-law-portfolio-checklist.xlsx
@@ -428,13 +428,13 @@
     <t>檢查一下是不是這段時間都在寫內容、沒有回頭處理缺口。內容寫得再多，缺的那幾項還是缺。</t>
   </si>
   <si>
-    <t>搭配文章：法政備審怎麼準備，CV、自傳與研究計畫的分工　https://tbd-web.vercel.app/pages/resources/law-graduate-cv.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-law-portfolio-checklist</t>
+    <t>搭配文章：法政備審怎麼準備，CV、自傳與研究計畫的分工　https://tbd-edu.com/pages/resources/law-graduate-cv.html?utm_source=tbd-web&amp;utm_medium=template&amp;utm_campaign=grad-law-portfolio-checklist</t>
   </si>
   <si>
     <t>上一階段是研究計畫書、下一階段是口試。備審裡的每一句話，口試時都可能被追問細節。</t>
   </si>
   <si>
-    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-web.vercel.app/pages/resources/tools.html</t>
+    <t>TBD Studio ｜ 研究所申請陪跑計畫　https://tbd-edu.com/pages/resources/tools.html</t>
   </si>
   <si>
     <t>第一段　經歷盤點</t>
